--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/4763-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/4763-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{03321415-2579-4760-B696-669F83A35F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6232A34A-BFBA-4001-AA6C-8892FBABFA36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{0CFD8F72-E840-4394-9E76-A7CBE8F8C2EA}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{5D8B1AF4-59DF-4287-91A2-BCD0189EA9AB}"/>
   </bookViews>
   <sheets>
     <sheet name="4763-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1535,25 +1535,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EB7AED1-9C61-4982-B230-7832284FBF18}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27857746-2A6A-458E-B5B2-A7ABDE100C5A}">
   <dimension ref="A1:R34"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" customWidth="1"/>
-    <col min="5" max="5" width="7.44140625" customWidth="1"/>
-    <col min="6" max="7" width="7.6640625" customWidth="1"/>
-    <col min="8" max="8" width="7.44140625" customWidth="1"/>
-    <col min="9" max="10" width="7.6640625" customWidth="1"/>
-    <col min="11" max="13" width="7.44140625" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" customWidth="1"/>
-    <col min="15" max="17" width="7.44140625" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="14.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="9.75" customWidth="1"/>
+    <col min="5" max="5" width="9.25" customWidth="1"/>
+    <col min="6" max="7" width="9.75" customWidth="1"/>
+    <col min="8" max="8" width="9.25" customWidth="1"/>
+    <col min="9" max="10" width="9.75" customWidth="1"/>
+    <col min="11" max="13" width="9.25" customWidth="1"/>
+    <col min="14" max="14" width="9.75" customWidth="1"/>
+    <col min="15" max="17" width="9.25" customWidth="1"/>
+    <col min="18" max="18" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1581,7 +1581,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1611,7 +1611,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1707,7 +1707,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="41">
         <v>2025</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1927,7 +1927,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="39">
         <v>2024</v>
       </c>
@@ -1981,7 +1981,7 @@
         <v>3.23</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>26</v>
       </c>
@@ -2037,7 +2037,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
@@ -2093,7 +2093,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="41">
         <v>2023</v>
       </c>
@@ -2147,7 +2147,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>26</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>26</v>
       </c>
@@ -2259,7 +2259,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="39">
         <v>2022</v>
       </c>
@@ -2313,7 +2313,7 @@
         <v>6.15</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>26</v>
       </c>
@@ -2369,7 +2369,7 @@
         <v>2.2400000000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>26</v>
       </c>
@@ -2425,7 +2425,7 @@
         <v>3.91</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="41">
         <v>2021</v>
       </c>
@@ -2535,7 +2535,7 @@
         <v>5.78</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>26</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="43" t="s">
         <v>26</v>
       </c>
@@ -2647,7 +2647,7 @@
         <v>5.78</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="44"/>
       <c r="B22" s="22" t="s">
         <v>44</v>
@@ -2669,7 +2669,7 @@
       <c r="Q22" s="48"/>
       <c r="R22" s="48"/>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>26</v>
       </c>
@@ -2725,7 +2725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="39">
         <v>2020</v>
       </c>
@@ -2779,7 +2779,7 @@
         <v>3.71</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>26</v>
       </c>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -2891,7 +2891,7 @@
         <v>3.71</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="41">
         <v>2019</v>
       </c>
@@ -2945,7 +2945,7 @@
         <v>3.36</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
         <v>26</v>
       </c>
@@ -3001,7 +3001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
         <v>26</v>
       </c>
@@ -3057,7 +3057,7 @@
         <v>3.36</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2018</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>3.89</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="41">
         <v>2017</v>
       </c>
@@ -3165,7 +3165,7 @@
         <v>2.79</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="39">
         <v>2016</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="41">
         <v>2015</v>
       </c>
@@ -3273,7 +3273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="39" t="s">
         <v>51</v>
       </c>
